--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run1/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run1/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -811,769 +811,778 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.7821,0.0721,0.1124,0.0429</t>
-  </si>
-  <si>
-    <t>0.0201,0.0137,0.0005,0.9899</t>
-  </si>
-  <si>
-    <t>0.7096,0.0251,0.0294,0.2721</t>
-  </si>
-  <si>
-    <t>0.0552,0.0186,0.0023,0.9729</t>
-  </si>
-  <si>
-    <t>0.9808,0.0213,0.0011,0.0009</t>
-  </si>
-  <si>
-    <t>0.9872,0.0059,0.0016,0.0024</t>
-  </si>
-  <si>
-    <t>0.9757,0.0215,0.0066,0.0012</t>
-  </si>
-  <si>
-    <t>0.9924,0.0027,0.0003,0.0016</t>
-  </si>
-  <si>
-    <t>0.9635,0.0452,0.0057,0.0023</t>
-  </si>
-  <si>
-    <t>0.9892,0.0055,0.0008,0.0019</t>
-  </si>
-  <si>
-    <t>0.9917,0.0027,0.0004,0.0020</t>
-  </si>
-  <si>
-    <t>0.9954,0.0010,0.0002,0.0013</t>
-  </si>
-  <si>
-    <t>0.6114,0.0464,0.4794,0.0025</t>
-  </si>
-  <si>
-    <t>0.2776,0.1251,0.6498,0.0023</t>
-  </si>
-  <si>
-    <t>0.2167,0.0964,0.7559,0.0012</t>
-  </si>
-  <si>
-    <t>0.1665,0.0162,0.8517,0.0077</t>
-  </si>
-  <si>
-    <t>0.8112,0.0258,0.2759,0.0046</t>
-  </si>
-  <si>
-    <t>0.0646,0.9432,0.0106,0.0013</t>
-  </si>
-  <si>
-    <t>0.0874,0.9341,0.0045,0.0013</t>
-  </si>
-  <si>
-    <t>0.6173,0.5085,0.0163,0.0057</t>
-  </si>
-  <si>
-    <t>0.3962,0.7123,0.0083,0.0046</t>
-  </si>
-  <si>
-    <t>0.0366,0.9644,0.0108,0.0013</t>
-  </si>
-  <si>
-    <t>0.5375,0.0307,0.5153,0.0141</t>
-  </si>
-  <si>
-    <t>0.5769,0.0564,0.4059,0.0323</t>
-  </si>
-  <si>
-    <t>0.0647,0.0087,0.9390,0.0057</t>
-  </si>
-  <si>
-    <t>0.2663,0.0248,0.7867,0.0116</t>
-  </si>
-  <si>
-    <t>0.1227,0.0096,0.9303,0.0016</t>
-  </si>
-  <si>
-    <t>0.2746,0.0204,0.8539,0.0023</t>
-  </si>
-  <si>
-    <t>0.0556,0.0053,0.9566,0.0114</t>
-  </si>
-  <si>
-    <t>0.2017,0.8128,0.0235,0.0096</t>
-  </si>
-  <si>
-    <t>0.3659,0.4062,0.2561,0.0033</t>
-  </si>
-  <si>
-    <t>0.0015,0.0082,0.9955,0.0013</t>
-  </si>
-  <si>
-    <t>0.0372,0.7447,0.4331,0.0006</t>
-  </si>
-  <si>
-    <t>0.7797,0.1837,0.0522,0.0147</t>
-  </si>
-  <si>
-    <t>0.3521,0.1390,0.6157,0.0073</t>
-  </si>
-  <si>
-    <t>0.3205,0.7688,0.0109,0.0048</t>
-  </si>
-  <si>
-    <t>0.1043,0.9050,0.0183,0.0039</t>
-  </si>
-  <si>
-    <t>0.0546,0.7666,0.5283,0.0076</t>
-  </si>
-  <si>
-    <t>0.2040,0.2519,0.6682,0.0451</t>
-  </si>
-  <si>
-    <t>0.1070,0.1828,0.8390,0.0094</t>
-  </si>
-  <si>
-    <t>0.4289,0.0276,0.5991,0.0393</t>
-  </si>
-  <si>
-    <t>0.0987,0.4596,0.6064,0.0093</t>
-  </si>
-  <si>
-    <t>0.0113,0.9572,0.0491,0.0007</t>
-  </si>
-  <si>
-    <t>0.0891,0.0548,0.9037,0.0030</t>
-  </si>
-  <si>
-    <t>0.0231,0.7521,0.0124,0.7691</t>
-  </si>
-  <si>
-    <t>0.0027,0.9791,0.0068,0.0494</t>
-  </si>
-  <si>
-    <t>0.0047,0.9774,0.0432,0.0051</t>
-  </si>
-  <si>
-    <t>0.0013,0.9924,0.0065,0.0119</t>
-  </si>
-  <si>
-    <t>0.0283,0.5302,0.8681,0.0016</t>
-  </si>
-  <si>
-    <t>0.0152,0.5428,0.9125,0.0012</t>
-  </si>
-  <si>
-    <t>0.2934,0.0158,0.7896,0.0047</t>
-  </si>
-  <si>
-    <t>0.0882,0.0133,0.9423,0.0014</t>
-  </si>
-  <si>
-    <t>0.0048,0.0140,0.9875,0.0027</t>
-  </si>
-  <si>
-    <t>0.0410,0.0387,0.9375,0.0022</t>
-  </si>
-  <si>
-    <t>0.9537,0.0616,0.0087,0.0013</t>
-  </si>
-  <si>
-    <t>0.9842,0.0089,0.0013,0.0027</t>
-  </si>
-  <si>
-    <t>0.9796,0.0105,0.0077,0.0011</t>
-  </si>
-  <si>
-    <t>0.0647,0.0625,0.9430,0.0043</t>
-  </si>
-  <si>
-    <t>0.9813,0.0048,0.0012,0.0063</t>
-  </si>
-  <si>
-    <t>0.9859,0.0088,0.0035,0.0011</t>
-  </si>
-  <si>
-    <t>0.9730,0.0185,0.0035,0.0037</t>
-  </si>
-  <si>
-    <t>0.0019,0.9556,0.7617,0.0001</t>
-  </si>
-  <si>
-    <t>0.0086,0.0631,0.9780,0.0017</t>
-  </si>
-  <si>
-    <t>0.2249,0.1033,0.7312,0.0121</t>
-  </si>
-  <si>
-    <t>0.0039,0.7247,0.9411,0.0004</t>
-  </si>
-  <si>
-    <t>0.0164,0.0339,0.9797,0.0004</t>
-  </si>
-  <si>
-    <t>0.0200,0.9614,0.0283,0.0034</t>
-  </si>
-  <si>
-    <t>0.0014,0.9958,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.7230,0.0609,0.3311,0.0038</t>
-  </si>
-  <si>
-    <t>0.5575,0.1540,0.4083,0.0103</t>
-  </si>
-  <si>
-    <t>0.0645,0.2130,0.8513,0.0019</t>
-  </si>
-  <si>
-    <t>0.0018,0.9820,0.2610,0.0001</t>
-  </si>
-  <si>
-    <t>0.0035,0.8637,0.8271,0.0005</t>
-  </si>
-  <si>
-    <t>0.0028,0.9822,0.1122,0.0029</t>
-  </si>
-  <si>
-    <t>0.0026,0.9711,0.4088,0.0002</t>
-  </si>
-  <si>
-    <t>0.0223,0.0008,0.0071,0.9766</t>
-  </si>
-  <si>
-    <t>0.0044,0.0118,0.0010,0.9956</t>
-  </si>
-  <si>
-    <t>0.0138,0.0015,0.0016,0.9912</t>
-  </si>
-  <si>
-    <t>0.0226,0.0038,0.0030,0.9841</t>
-  </si>
-  <si>
-    <t>0.0632,0.0071,0.0079,0.9626</t>
-  </si>
-  <si>
-    <t>0.0114,0.0047,0.0024,0.9915</t>
-  </si>
-  <si>
-    <t>0.0006,0.9791,0.8486,0.0006</t>
-  </si>
-  <si>
-    <t>0.0038,0.8178,0.9109,0.0004</t>
-  </si>
-  <si>
-    <t>0.0196,0.7345,0.6373,0.0009</t>
-  </si>
-  <si>
-    <t>0.0228,0.5072,0.8346,0.0041</t>
-  </si>
-  <si>
-    <t>0.0010,0.9666,0.7301,0.0001</t>
-  </si>
-  <si>
-    <t>0.0046,0.9621,0.2109,0.0004</t>
-  </si>
-  <si>
-    <t>0.9814,0.0149,0.0050,0.0010</t>
-  </si>
-  <si>
-    <t>0.9774,0.0156,0.0044,0.0022</t>
-  </si>
-  <si>
-    <t>0.9779,0.0261,0.0019,0.0007</t>
-  </si>
-  <si>
-    <t>0.9881,0.0052,0.0007,0.0026</t>
-  </si>
-  <si>
-    <t>0.9819,0.0122,0.0038,0.0013</t>
-  </si>
-  <si>
-    <t>0.9934,0.0027,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.9718,0.0145,0.0013,0.0074</t>
-  </si>
-  <si>
-    <t>0.9587,0.0319,0.0048,0.0053</t>
-  </si>
-  <si>
-    <t>0.9919,0.0026,0.0004,0.0018</t>
-  </si>
-  <si>
-    <t>0.9839,0.0102,0.0026,0.0021</t>
-  </si>
-  <si>
-    <t>0.9842,0.0097,0.0049,0.0013</t>
-  </si>
-  <si>
-    <t>0.9906,0.0054,0.0007,0.0008</t>
-  </si>
-  <si>
-    <t>0.9874,0.0046,0.0013,0.0030</t>
-  </si>
-  <si>
-    <t>0.9897,0.0068,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9948,0.0016,0.0001,0.0013</t>
-  </si>
-  <si>
-    <t>0.9793,0.0119,0.0033,0.0029</t>
-  </si>
-  <si>
-    <t>0.0130,0.0038,0.9844,0.0073</t>
-  </si>
-  <si>
-    <t>0.4485,0.1023,0.4810,0.0223</t>
-  </si>
-  <si>
-    <t>0.7252,0.0290,0.3187,0.0126</t>
-  </si>
-  <si>
-    <t>0.0495,0.0206,0.9426,0.0016</t>
-  </si>
-  <si>
-    <t>0.3886,0.7579,0.0050,0.0010</t>
-  </si>
-  <si>
-    <t>0.0662,0.9398,0.0101,0.0029</t>
-  </si>
-  <si>
-    <t>0.3608,0.7657,0.0056,0.0013</t>
-  </si>
-  <si>
-    <t>0.3940,0.7111,0.0072,0.0031</t>
-  </si>
-  <si>
-    <t>0.1795,0.8834,0.0031,0.0014</t>
-  </si>
-  <si>
-    <t>0.0206,0.9735,0.0095,0.0003</t>
-  </si>
-  <si>
-    <t>0.8094,0.2569,0.0128,0.0031</t>
-  </si>
-  <si>
-    <t>0.8326,0.0644,0.0871,0.0121</t>
-  </si>
-  <si>
-    <t>0.2917,0.0793,0.6580,0.0054</t>
-  </si>
-  <si>
-    <t>0.6275,0.2141,0.1217,0.0235</t>
-  </si>
-  <si>
-    <t>0.3976,0.2502,0.3876,0.0186</t>
-  </si>
-  <si>
-    <t>0.6030,0.2095,0.1855,0.0550</t>
-  </si>
-  <si>
-    <t>0.0011,0.9950,0.0021,0.0022</t>
-  </si>
-  <si>
-    <t>0.0048,0.9759,0.1022,0.0087</t>
-  </si>
-  <si>
-    <t>0.0769,0.8882,0.0128,0.0395</t>
-  </si>
-  <si>
-    <t>0.0037,0.9847,0.0371,0.0064</t>
-  </si>
-  <si>
-    <t>0.0550,0.9304,0.0396,0.0017</t>
-  </si>
-  <si>
-    <t>0.6904,0.4313,0.0244,0.0027</t>
-  </si>
-  <si>
-    <t>0.3551,0.7424,0.0102,0.0034</t>
-  </si>
-  <si>
-    <t>0.9671,0.0196,0.0043,0.0053</t>
-  </si>
-  <si>
-    <t>0.9830,0.0121,0.0025,0.0014</t>
-  </si>
-  <si>
-    <t>0.9895,0.0033,0.0012,0.0024</t>
-  </si>
-  <si>
-    <t>0.9720,0.0101,0.0055,0.0056</t>
-  </si>
-  <si>
-    <t>0.9840,0.0066,0.0013,0.0032</t>
-  </si>
-  <si>
-    <t>0.9201,0.0889,0.0154,0.0048</t>
-  </si>
-  <si>
-    <t>0.9692,0.0166,0.0067,0.0052</t>
-  </si>
-  <si>
-    <t>0.9703,0.0244,0.0028,0.0035</t>
-  </si>
-  <si>
-    <t>0.0091,0.8544,0.7284,0.0009</t>
-  </si>
-  <si>
-    <t>0.0168,0.5327,0.8616,0.0010</t>
-  </si>
-  <si>
-    <t>0.1042,0.2040,0.7495,0.0016</t>
-  </si>
-  <si>
-    <t>0.0558,0.1034,0.8979,0.0009</t>
-  </si>
-  <si>
-    <t>0.7980,0.0421,0.1382,0.0193</t>
-  </si>
-  <si>
-    <t>0.6729,0.0980,0.2592,0.0124</t>
-  </si>
-  <si>
-    <t>0.1830,0.0479,0.8635,0.0032</t>
-  </si>
-  <si>
-    <t>0.6914,0.2030,0.0880,0.0080</t>
-  </si>
-  <si>
-    <t>0.1198,0.0026,0.0109,0.9099</t>
-  </si>
-  <si>
-    <t>0.0014,0.0042,0.0007,0.9983</t>
-  </si>
-  <si>
-    <t>0.0044,0.0017,0.0025,0.9949</t>
-  </si>
-  <si>
-    <t>0.0282,0.0040,0.0067,0.9800</t>
-  </si>
-  <si>
-    <t>0.0006,0.9752,0.4480,0.0059</t>
-  </si>
-  <si>
-    <t>0.9251,0.0807,0.0126,0.0023</t>
-  </si>
-  <si>
-    <t>0.7022,0.3785,0.0088,0.0058</t>
-  </si>
-  <si>
-    <t>0.9628,0.0198,0.0085,0.0038</t>
-  </si>
-  <si>
-    <t>0.2589,0.5640,0.1437,0.0009</t>
-  </si>
-  <si>
-    <t>0.9615,0.0161,0.0152,0.0058</t>
-  </si>
-  <si>
-    <t>0.7425,0.0237,0.1379,0.1150</t>
-  </si>
-  <si>
-    <t>0.9438,0.0446,0.0035,0.0062</t>
-  </si>
-  <si>
-    <t>0.0780,0.0347,0.6589,0.3942</t>
-  </si>
-  <si>
-    <t>0.8378,0.0054,0.0228,0.1059</t>
-  </si>
-  <si>
-    <t>0.9048,0.0389,0.0300,0.0224</t>
-  </si>
-  <si>
-    <t>0.4783,0.5166,0.0711,0.0179</t>
-  </si>
-  <si>
-    <t>0.8586,0.0862,0.0513,0.0087</t>
-  </si>
-  <si>
-    <t>0.5633,0.5187,0.0123,0.0112</t>
-  </si>
-  <si>
-    <t>0.5180,0.4528,0.0703,0.0253</t>
-  </si>
-  <si>
-    <t>0.6950,0.2239,0.1309,0.0084</t>
-  </si>
-  <si>
-    <t>0.8587,0.0921,0.0225,0.0063</t>
-  </si>
-  <si>
-    <t>0.9784,0.0127,0.0062,0.0022</t>
-  </si>
-  <si>
-    <t>0.9751,0.0198,0.0012,0.0027</t>
-  </si>
-  <si>
-    <t>0.9919,0.0020,0.0009,0.0016</t>
-  </si>
-  <si>
-    <t>0.9848,0.0065,0.0016,0.0037</t>
-  </si>
-  <si>
-    <t>0.9885,0.0031,0.0013,0.0027</t>
-  </si>
-  <si>
-    <t>0.9740,0.0178,0.0071,0.0027</t>
-  </si>
-  <si>
-    <t>0.9876,0.0068,0.0027,0.0007</t>
-  </si>
-  <si>
-    <t>0.9906,0.0041,0.0010,0.0011</t>
-  </si>
-  <si>
-    <t>0.7132,0.3847,0.0158,0.0041</t>
-  </si>
-  <si>
-    <t>0.9236,0.0926,0.0062,0.0020</t>
-  </si>
-  <si>
-    <t>0.6943,0.4512,0.0076,0.0026</t>
-  </si>
-  <si>
-    <t>0.6220,0.2053,0.3523,0.0058</t>
-  </si>
-  <si>
-    <t>0.9000,0.1423,0.0052,0.0024</t>
-  </si>
-  <si>
-    <t>0.9183,0.0630,0.0109,0.0077</t>
-  </si>
-  <si>
-    <t>0.9762,0.0145,0.0034,0.0025</t>
-  </si>
-  <si>
-    <t>0.9499,0.0431,0.0040,0.0054</t>
-  </si>
-  <si>
-    <t>0.0021,0.0498,0.9949,0.0001</t>
-  </si>
-  <si>
-    <t>0.9525,0.0459,0.0081,0.0015</t>
-  </si>
-  <si>
-    <t>0.0050,0.0048,0.9927,0.0013</t>
-  </si>
-  <si>
-    <t>0.0166,0.1437,0.9532,0.0017</t>
-  </si>
-  <si>
-    <t>0.0918,0.0399,0.8977,0.0094</t>
-  </si>
-  <si>
-    <t>0.0408,0.2065,0.9057,0.0058</t>
-  </si>
-  <si>
-    <t>0.0531,0.0172,0.9540,0.0020</t>
-  </si>
-  <si>
-    <t>0.0065,0.0062,0.9941,0.0003</t>
-  </si>
-  <si>
-    <t>0.0230,0.0148,0.9646,0.0039</t>
-  </si>
-  <si>
-    <t>0.2037,0.0189,0.8761,0.0034</t>
-  </si>
-  <si>
-    <t>0.1679,0.0893,0.7814,0.0101</t>
-  </si>
-  <si>
-    <t>0.3797,0.3352,0.3376,0.0280</t>
-  </si>
-  <si>
-    <t>0.1670,0.6192,0.1561,0.0010</t>
-  </si>
-  <si>
-    <t>0.2324,0.5952,0.2351,0.0213</t>
-  </si>
-  <si>
-    <t>0.4312,0.4792,0.1344,0.0136</t>
-  </si>
-  <si>
-    <t>0.6689,0.0394,0.3792,0.0213</t>
-  </si>
-  <si>
-    <t>0.5423,0.0659,0.4704,0.0030</t>
-  </si>
-  <si>
-    <t>0.8525,0.1948,0.0115,0.0016</t>
-  </si>
-  <si>
-    <t>0.8720,0.1959,0.0059,0.0026</t>
-  </si>
-  <si>
-    <t>0.5820,0.5458,0.0121,0.0043</t>
-  </si>
-  <si>
-    <t>0.9333,0.0726,0.0028,0.0046</t>
-  </si>
-  <si>
-    <t>0.9340,0.0916,0.0019,0.0019</t>
-  </si>
-  <si>
-    <t>0.5964,0.0586,0.4556,0.0096</t>
-  </si>
-  <si>
-    <t>0.7840,0.0209,0.2488,0.0110</t>
-  </si>
-  <si>
-    <t>0.6130,0.0734,0.3058,0.0944</t>
-  </si>
-  <si>
-    <t>0.6418,0.1157,0.2499,0.0391</t>
-  </si>
-  <si>
-    <t>0.8521,0.0099,0.1806,0.0072</t>
-  </si>
-  <si>
-    <t>0.0360,0.0278,0.9082,0.0754</t>
-  </si>
-  <si>
-    <t>0.0788,0.0560,0.8706,0.0372</t>
-  </si>
-  <si>
-    <t>0.0833,0.4087,0.8179,0.0102</t>
-  </si>
-  <si>
-    <t>0.1612,0.1254,0.7805,0.0067</t>
-  </si>
-  <si>
-    <t>0.0413,0.6232,0.5326,0.0008</t>
-  </si>
-  <si>
-    <t>0.9738,0.0054,0.0003,0.0101</t>
-  </si>
-  <si>
-    <t>0.9857,0.0095,0.0018,0.0014</t>
-  </si>
-  <si>
-    <t>0.9812,0.0061,0.0004,0.0046</t>
-  </si>
-  <si>
-    <t>0.9894,0.0066,0.0011,0.0014</t>
-  </si>
-  <si>
-    <t>0.9789,0.0211,0.0010,0.0013</t>
-  </si>
-  <si>
-    <t>0.9655,0.0333,0.0031,0.0025</t>
-  </si>
-  <si>
-    <t>0.9778,0.0065,0.0035,0.0066</t>
-  </si>
-  <si>
-    <t>0.9863,0.0030,0.0005,0.0045</t>
-  </si>
-  <si>
-    <t>0.2037,0.0368,0.8460,0.0024</t>
-  </si>
-  <si>
-    <t>0.2462,0.5514,0.2672,0.0055</t>
-  </si>
-  <si>
-    <t>0.8062,0.1386,0.0320,0.0337</t>
-  </si>
-  <si>
-    <t>0.0196,0.0124,0.9824,0.0007</t>
-  </si>
-  <si>
-    <t>0.0064,0.1242,0.9759,0.0021</t>
-  </si>
-  <si>
-    <t>0.0300,0.5464,0.7037,0.0026</t>
-  </si>
-  <si>
-    <t>0.0007,0.0069,0.9973,0.0004</t>
-  </si>
-  <si>
-    <t>0.1587,0.0251,0.8827,0.0020</t>
-  </si>
-  <si>
-    <t>0.0179,0.0239,0.9863,0.0004</t>
-  </si>
-  <si>
-    <t>0.0108,0.0090,0.9791,0.0047</t>
-  </si>
-  <si>
-    <t>0.4639,0.1397,0.4125,0.0092</t>
-  </si>
-  <si>
-    <t>0.5798,0.0380,0.4815,0.0070</t>
-  </si>
-  <si>
-    <t>0.6328,0.0316,0.5210,0.0067</t>
-  </si>
-  <si>
-    <t>0.8227,0.0170,0.0820,0.0630</t>
-  </si>
-  <si>
-    <t>0.9504,0.0313,0.0013,0.0074</t>
-  </si>
-  <si>
-    <t>0.9816,0.0112,0.0016,0.0030</t>
-  </si>
-  <si>
-    <t>0.9765,0.0184,0.0057,0.0015</t>
-  </si>
-  <si>
-    <t>0.9817,0.0109,0.0023,0.0019</t>
-  </si>
-  <si>
-    <t>0.9837,0.0077,0.0014,0.0030</t>
-  </si>
-  <si>
-    <t>0.9854,0.0175,0.0014,0.0005</t>
-  </si>
-  <si>
-    <t>0.9898,0.0042,0.0009,0.0021</t>
-  </si>
-  <si>
-    <t>0.9779,0.0212,0.0012,0.0018</t>
-  </si>
-  <si>
-    <t>0.0227,0.3330,0.8164,0.0022</t>
-  </si>
-  <si>
-    <t>0.0320,0.4339,0.7958,0.0225</t>
-  </si>
-  <si>
-    <t>0.0073,0.9340,0.3383,0.0009</t>
-  </si>
-  <si>
-    <t>0.0366,0.1682,0.8909,0.0042</t>
-  </si>
-  <si>
-    <t>0.0624,0.0044,0.9629,0.0040</t>
-  </si>
-  <si>
-    <t>0.0676,0.0188,0.9224,0.0192</t>
-  </si>
-  <si>
-    <t>0.5854,0.0769,0.3826,0.0317</t>
-  </si>
-  <si>
-    <t>0.3432,0.0139,0.7184,0.0236</t>
-  </si>
-  <si>
-    <t>0.8913,0.0039,0.0111,0.0814</t>
-  </si>
-  <si>
-    <t>0.0177,0.0489,0.0030,0.9849</t>
-  </si>
-  <si>
-    <t>0.1222,0.0080,0.0053,0.9293</t>
-  </si>
-  <si>
-    <t>0.0053,0.0003,0.0002,0.9974</t>
-  </si>
-  <si>
-    <t>0.0112,0.0088,0.0002,0.9941</t>
-  </si>
-  <si>
-    <t>0.7307,0.0316,0.1078,0.1224</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.7763,0.0417,0.0196,0.1464</t>
+  </si>
+  <si>
+    <t>0.0159,0.0259,0.0007,0.9879</t>
+  </si>
+  <si>
+    <t>0.3165,0.0719,0.0110,0.7031</t>
+  </si>
+  <si>
+    <t>0.0234,0.0041,0.0009,0.9898</t>
+  </si>
+  <si>
+    <t>0.9904,0.0070,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.9884,0.0047,0.0024,0.0018</t>
+  </si>
+  <si>
+    <t>0.9905,0.0076,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9877,0.0086,0.0011,0.0015</t>
+  </si>
+  <si>
+    <t>0.9778,0.0188,0.0016,0.0033</t>
+  </si>
+  <si>
+    <t>0.9922,0.0040,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9932,0.0042,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9921,0.0038,0.0005,0.0012</t>
+  </si>
+  <si>
+    <t>0.6325,0.0522,0.4157,0.0075</t>
+  </si>
+  <si>
+    <t>0.0471,0.0375,0.9410,0.0033</t>
+  </si>
+  <si>
+    <t>0.1889,0.0856,0.8000,0.0014</t>
+  </si>
+  <si>
+    <t>0.0311,0.0385,0.9485,0.0023</t>
+  </si>
+  <si>
+    <t>0.7212,0.0395,0.3515,0.0087</t>
+  </si>
+  <si>
+    <t>0.0325,0.9599,0.0170,0.0006</t>
+  </si>
+  <si>
+    <t>0.1095,0.9188,0.0098,0.0006</t>
+  </si>
+  <si>
+    <t>0.2062,0.8372,0.0298,0.0017</t>
+  </si>
+  <si>
+    <t>0.2548,0.8175,0.0120,0.0013</t>
+  </si>
+  <si>
+    <t>0.1506,0.8753,0.0242,0.0006</t>
+  </si>
+  <si>
+    <t>0.6824,0.0205,0.3947,0.0165</t>
+  </si>
+  <si>
+    <t>0.6602,0.0179,0.2957,0.0550</t>
+  </si>
+  <si>
+    <t>0.0475,0.0066,0.9598,0.0063</t>
+  </si>
+  <si>
+    <t>0.3421,0.0168,0.7913,0.0064</t>
+  </si>
+  <si>
+    <t>0.2961,0.0948,0.6631,0.0080</t>
+  </si>
+  <si>
+    <t>0.2095,0.0059,0.9150,0.0009</t>
+  </si>
+  <si>
+    <t>0.0914,0.0068,0.9275,0.0153</t>
+  </si>
+  <si>
+    <t>0.0640,0.9283,0.0084,0.0123</t>
+  </si>
+  <si>
+    <t>0.6180,0.1835,0.2523,0.0150</t>
+  </si>
+  <si>
+    <t>0.0210,0.0128,0.9700,0.0088</t>
+  </si>
+  <si>
+    <t>0.0371,0.8561,0.1408,0.0014</t>
+  </si>
+  <si>
+    <t>0.8791,0.0924,0.0303,0.0150</t>
+  </si>
+  <si>
+    <t>0.5611,0.2187,0.1843,0.0023</t>
+  </si>
+  <si>
+    <t>0.8924,0.1641,0.0062,0.0027</t>
+  </si>
+  <si>
+    <t>0.1194,0.8586,0.0794,0.0042</t>
+  </si>
+  <si>
+    <t>0.0951,0.5130,0.6772,0.0084</t>
+  </si>
+  <si>
+    <t>0.1439,0.0355,0.9101,0.0020</t>
+  </si>
+  <si>
+    <t>0.2122,0.1439,0.7139,0.0403</t>
+  </si>
+  <si>
+    <t>0.1960,0.0195,0.7341,0.0672</t>
+  </si>
+  <si>
+    <t>0.0555,0.0560,0.9329,0.0011</t>
+  </si>
+  <si>
+    <t>0.0046,0.9811,0.0370,0.0004</t>
+  </si>
+  <si>
+    <t>0.0254,0.0966,0.9336,0.0053</t>
+  </si>
+  <si>
+    <t>0.0279,0.5809,0.0405,0.8594</t>
+  </si>
+  <si>
+    <t>0.0173,0.9578,0.0521,0.0149</t>
+  </si>
+  <si>
+    <t>0.0126,0.9638,0.0130,0.0176</t>
+  </si>
+  <si>
+    <t>0.0020,0.9905,0.0068,0.0112</t>
+  </si>
+  <si>
+    <t>0.0553,0.4918,0.7507,0.0041</t>
+  </si>
+  <si>
+    <t>0.0669,0.3317,0.8270,0.0070</t>
+  </si>
+  <si>
+    <t>0.0706,0.0225,0.9229,0.0054</t>
+  </si>
+  <si>
+    <t>0.0446,0.0064,0.9695,0.0012</t>
+  </si>
+  <si>
+    <t>0.0061,0.0155,0.9829,0.0043</t>
+  </si>
+  <si>
+    <t>0.0995,0.1971,0.7492,0.0049</t>
+  </si>
+  <si>
+    <t>0.9417,0.0572,0.0073,0.0038</t>
+  </si>
+  <si>
+    <t>0.9439,0.0472,0.0161,0.0039</t>
+  </si>
+  <si>
+    <t>0.9735,0.0217,0.0053,0.0015</t>
+  </si>
+  <si>
+    <t>0.0436,0.1095,0.9461,0.0010</t>
+  </si>
+  <si>
+    <t>0.9822,0.0084,0.0036,0.0013</t>
+  </si>
+  <si>
+    <t>0.9796,0.0123,0.0033,0.0027</t>
+  </si>
+  <si>
+    <t>0.9748,0.0201,0.0046,0.0011</t>
+  </si>
+  <si>
+    <t>0.0084,0.7910,0.8377,0.0014</t>
+  </si>
+  <si>
+    <t>0.0176,0.0760,0.9486,0.0029</t>
+  </si>
+  <si>
+    <t>0.0299,0.2358,0.8769,0.0149</t>
+  </si>
+  <si>
+    <t>0.0021,0.9006,0.8857,0.0004</t>
+  </si>
+  <si>
+    <t>0.0189,0.0087,0.9761,0.0040</t>
+  </si>
+  <si>
+    <t>0.0073,0.9744,0.0220,0.0002</t>
+  </si>
+  <si>
+    <t>0.0065,0.9883,0.0019,0.0003</t>
+  </si>
+  <si>
+    <t>0.8194,0.0341,0.2617,0.0062</t>
+  </si>
+  <si>
+    <t>0.4776,0.2643,0.3691,0.0154</t>
+  </si>
+  <si>
+    <t>0.0586,0.6994,0.2173,0.0053</t>
+  </si>
+  <si>
+    <t>0.0151,0.8302,0.5377,0.0010</t>
+  </si>
+  <si>
+    <t>0.0023,0.9209,0.8422,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.9801,0.3685,0.0015</t>
+  </si>
+  <si>
+    <t>0.0061,0.9430,0.4305,0.0007</t>
+  </si>
+  <si>
+    <t>0.0705,0.0002,0.0023,0.9555</t>
+  </si>
+  <si>
+    <t>0.0146,0.0102,0.0008,0.9915</t>
+  </si>
+  <si>
+    <t>0.0073,0.0020,0.0003,0.9964</t>
+  </si>
+  <si>
+    <t>0.0935,0.0107,0.0018,0.9531</t>
+  </si>
+  <si>
+    <t>0.0557,0.0036,0.0086,0.9614</t>
+  </si>
+  <si>
+    <t>0.0088,0.0065,0.0013,0.9934</t>
+  </si>
+  <si>
+    <t>0.0011,0.9314,0.8401,0.0001</t>
+  </si>
+  <si>
+    <t>0.0021,0.8593,0.9297,0.0002</t>
+  </si>
+  <si>
+    <t>0.0046,0.8667,0.8011,0.0009</t>
+  </si>
+  <si>
+    <t>0.0060,0.7139,0.9227,0.0005</t>
+  </si>
+  <si>
+    <t>0.0014,0.9779,0.3987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0445,0.7019,0.5309,0.0044</t>
+  </si>
+  <si>
+    <t>0.9624,0.0465,0.0050,0.0016</t>
+  </si>
+  <si>
+    <t>0.9878,0.0031,0.0002,0.0030</t>
+  </si>
+  <si>
+    <t>0.9838,0.0216,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.9929,0.0028,0.0001,0.0013</t>
+  </si>
+  <si>
+    <t>0.9701,0.0343,0.0038,0.0009</t>
+  </si>
+  <si>
+    <t>0.9896,0.0031,0.0003,0.0031</t>
+  </si>
+  <si>
+    <t>0.9674,0.0355,0.0026,0.0025</t>
+  </si>
+  <si>
+    <t>0.9782,0.0255,0.0043,0.0011</t>
+  </si>
+  <si>
+    <t>0.9931,0.0027,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.9921,0.0053,0.0015,0.0006</t>
+  </si>
+  <si>
+    <t>0.9924,0.0040,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9942,0.0015,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.9881,0.0088,0.0031,0.0007</t>
+  </si>
+  <si>
+    <t>0.9739,0.0376,0.0017,0.0009</t>
+  </si>
+  <si>
+    <t>0.9925,0.0045,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9896,0.0035,0.0007,0.0022</t>
+  </si>
+  <si>
+    <t>0.0072,0.0071,0.9867,0.0057</t>
+  </si>
+  <si>
+    <t>0.2994,0.2130,0.4650,0.0583</t>
+  </si>
+  <si>
+    <t>0.8099,0.0195,0.1756,0.0153</t>
+  </si>
+  <si>
+    <t>0.1280,0.0122,0.9256,0.0018</t>
+  </si>
+  <si>
+    <t>0.1397,0.9017,0.0040,0.0027</t>
+  </si>
+  <si>
+    <t>0.2522,0.8248,0.0091,0.0029</t>
+  </si>
+  <si>
+    <t>0.2060,0.8429,0.0028,0.0034</t>
+  </si>
+  <si>
+    <t>0.7252,0.3889,0.0075,0.0046</t>
+  </si>
+  <si>
+    <t>0.0753,0.9500,0.0031,0.0006</t>
+  </si>
+  <si>
+    <t>0.0129,0.9814,0.0025,0.0010</t>
+  </si>
+  <si>
+    <t>0.6907,0.4487,0.0141,0.0031</t>
+  </si>
+  <si>
+    <t>0.6498,0.0661,0.3733,0.0219</t>
+  </si>
+  <si>
+    <t>0.4411,0.0129,0.7272,0.0101</t>
+  </si>
+  <si>
+    <t>0.5152,0.3466,0.1594,0.0124</t>
+  </si>
+  <si>
+    <t>0.3872,0.2629,0.3707,0.0361</t>
+  </si>
+  <si>
+    <t>0.4868,0.0635,0.0180,0.5335</t>
+  </si>
+  <si>
+    <t>0.0052,0.9849,0.0084,0.0044</t>
+  </si>
+  <si>
+    <t>0.0021,0.9874,0.0085,0.0098</t>
+  </si>
+  <si>
+    <t>0.0904,0.8818,0.0189,0.0246</t>
+  </si>
+  <si>
+    <t>0.0035,0.9867,0.0807,0.0010</t>
+  </si>
+  <si>
+    <t>0.0702,0.9192,0.0241,0.0035</t>
+  </si>
+  <si>
+    <t>0.7509,0.3495,0.0192,0.0050</t>
+  </si>
+  <si>
+    <t>0.4160,0.6586,0.0064,0.0116</t>
+  </si>
+  <si>
+    <t>0.9728,0.0180,0.0038,0.0026</t>
+  </si>
+  <si>
+    <t>0.9749,0.0058,0.0005,0.0096</t>
+  </si>
+  <si>
+    <t>0.9771,0.0057,0.0020,0.0073</t>
+  </si>
+  <si>
+    <t>0.9685,0.0104,0.0081,0.0076</t>
+  </si>
+  <si>
+    <t>0.9817,0.0116,0.0022,0.0022</t>
+  </si>
+  <si>
+    <t>0.9203,0.0503,0.0201,0.0108</t>
+  </si>
+  <si>
+    <t>0.9881,0.0040,0.0020,0.0020</t>
+  </si>
+  <si>
+    <t>0.9901,0.0074,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.0025,0.8345,0.9113,0.0009</t>
+  </si>
+  <si>
+    <t>0.0266,0.6406,0.8078,0.0014</t>
+  </si>
+  <si>
+    <t>0.0609,0.1176,0.8842,0.0034</t>
+  </si>
+  <si>
+    <t>0.1509,0.1205,0.7403,0.0021</t>
+  </si>
+  <si>
+    <t>0.6936,0.1859,0.0690,0.0158</t>
+  </si>
+  <si>
+    <t>0.8248,0.0433,0.1283,0.0067</t>
+  </si>
+  <si>
+    <t>0.3824,0.0123,0.7275,0.0209</t>
+  </si>
+  <si>
+    <t>0.7304,0.0602,0.2033,0.0367</t>
+  </si>
+  <si>
+    <t>0.1099,0.0025,0.0222,0.8926</t>
+  </si>
+  <si>
+    <t>0.0017,0.0050,0.0028,0.9966</t>
+  </si>
+  <si>
+    <t>0.0332,0.0230,0.0027,0.9808</t>
+  </si>
+  <si>
+    <t>0.0086,0.0045,0.0027,0.9924</t>
+  </si>
+  <si>
+    <t>0.0023,0.9245,0.8540,0.0008</t>
+  </si>
+  <si>
+    <t>0.9688,0.0309,0.0038,0.0014</t>
+  </si>
+  <si>
+    <t>0.4623,0.5860,0.0206,0.0033</t>
+  </si>
+  <si>
+    <t>0.9813,0.0054,0.0015,0.0041</t>
+  </si>
+  <si>
+    <t>0.5956,0.5277,0.0110,0.0009</t>
+  </si>
+  <si>
+    <t>0.9061,0.0507,0.0370,0.0112</t>
+  </si>
+  <si>
+    <t>0.7019,0.0052,0.0396,0.2227</t>
+  </si>
+  <si>
+    <t>0.9401,0.0307,0.0025,0.0096</t>
+  </si>
+  <si>
+    <t>0.0673,0.4669,0.5642,0.1651</t>
+  </si>
+  <si>
+    <t>0.9246,0.0016,0.0055,0.0559</t>
+  </si>
+  <si>
+    <t>0.9565,0.0104,0.0073,0.0121</t>
+  </si>
+  <si>
+    <t>0.6706,0.2825,0.0084,0.0356</t>
+  </si>
+  <si>
+    <t>0.8464,0.0885,0.0592,0.0045</t>
+  </si>
+  <si>
+    <t>0.5124,0.4992,0.0729,0.0241</t>
+  </si>
+  <si>
+    <t>0.4543,0.5763,0.0591,0.0074</t>
+  </si>
+  <si>
+    <t>0.7333,0.2015,0.0851,0.0039</t>
+  </si>
+  <si>
+    <t>0.8523,0.1042,0.0219,0.0054</t>
+  </si>
+  <si>
+    <t>0.9711,0.0183,0.0032,0.0043</t>
+  </si>
+  <si>
+    <t>0.9888,0.0104,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9901,0.0044,0.0009,0.0012</t>
+  </si>
+  <si>
+    <t>0.9807,0.0035,0.0015,0.0080</t>
+  </si>
+  <si>
+    <t>0.9756,0.0201,0.0042,0.0023</t>
+  </si>
+  <si>
+    <t>0.9610,0.0245,0.0096,0.0044</t>
+  </si>
+  <si>
+    <t>0.9781,0.0062,0.0053,0.0043</t>
+  </si>
+  <si>
+    <t>0.9922,0.0039,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.5122,0.6418,0.0092,0.0025</t>
+  </si>
+  <si>
+    <t>0.8186,0.2827,0.0095,0.0012</t>
+  </si>
+  <si>
+    <t>0.7829,0.3366,0.0087,0.0013</t>
+  </si>
+  <si>
+    <t>0.0416,0.2437,0.9385,0.0006</t>
+  </si>
+  <si>
+    <t>0.8260,0.2781,0.0071,0.0023</t>
+  </si>
+  <si>
+    <t>0.8976,0.0954,0.0193,0.0027</t>
+  </si>
+  <si>
+    <t>0.9579,0.0472,0.0080,0.0019</t>
+  </si>
+  <si>
+    <t>0.8775,0.1461,0.0176,0.0023</t>
+  </si>
+  <si>
+    <t>0.0098,0.0144,0.9919,0.0002</t>
+  </si>
+  <si>
+    <t>0.9372,0.0612,0.0155,0.0031</t>
+  </si>
+  <si>
+    <t>0.0034,0.0199,0.9933,0.0004</t>
+  </si>
+  <si>
+    <t>0.0405,0.2433,0.8854,0.0053</t>
+  </si>
+  <si>
+    <t>0.0185,0.0864,0.9474,0.0066</t>
+  </si>
+  <si>
+    <t>0.0183,0.0832,0.9571,0.0046</t>
+  </si>
+  <si>
+    <t>0.1285,0.0074,0.9366,0.0011</t>
+  </si>
+  <si>
+    <t>0.0131,0.0025,0.9881,0.0014</t>
+  </si>
+  <si>
+    <t>0.0377,0.0228,0.9465,0.0050</t>
+  </si>
+  <si>
+    <t>0.2464,0.1087,0.6692,0.0294</t>
+  </si>
+  <si>
+    <t>0.4371,0.0630,0.6068,0.0029</t>
+  </si>
+  <si>
+    <t>0.7115,0.0732,0.2779,0.0090</t>
+  </si>
+  <si>
+    <t>0.3036,0.1724,0.5323,0.0030</t>
+  </si>
+  <si>
+    <t>0.2853,0.5452,0.1679,0.0048</t>
+  </si>
+  <si>
+    <t>0.2323,0.4757,0.2919,0.0076</t>
+  </si>
+  <si>
+    <t>0.6364,0.0988,0.2885,0.0311</t>
+  </si>
+  <si>
+    <t>0.5712,0.0771,0.4554,0.0076</t>
+  </si>
+  <si>
+    <t>0.5115,0.6554,0.0025,0.0017</t>
+  </si>
+  <si>
+    <t>0.8948,0.1267,0.0120,0.0049</t>
+  </si>
+  <si>
+    <t>0.7193,0.3855,0.0116,0.0015</t>
+  </si>
+  <si>
+    <t>0.9797,0.0223,0.0018,0.0008</t>
+  </si>
+  <si>
+    <t>0.8418,0.2367,0.0107,0.0029</t>
+  </si>
+  <si>
+    <t>0.6782,0.1339,0.1890,0.0269</t>
+  </si>
+  <si>
+    <t>0.8085,0.0231,0.2878,0.0044</t>
+  </si>
+  <si>
+    <t>0.7375,0.0222,0.2119,0.0544</t>
+  </si>
+  <si>
+    <t>0.4791,0.1114,0.4230,0.0463</t>
+  </si>
+  <si>
+    <t>0.7571,0.0783,0.1738,0.0071</t>
+  </si>
+  <si>
+    <t>0.0739,0.0252,0.8870,0.0551</t>
+  </si>
+  <si>
+    <t>0.0609,0.1401,0.8618,0.0092</t>
+  </si>
+  <si>
+    <t>0.0546,0.1531,0.8796,0.0073</t>
+  </si>
+  <si>
+    <t>0.1058,0.0659,0.8867,0.0052</t>
+  </si>
+  <si>
+    <t>0.0910,0.1971,0.7553,0.0033</t>
+  </si>
+  <si>
+    <t>0.9740,0.0055,0.0006,0.0115</t>
+  </si>
+  <si>
+    <t>0.9584,0.0416,0.0116,0.0014</t>
+  </si>
+  <si>
+    <t>0.9680,0.0098,0.0015,0.0129</t>
+  </si>
+  <si>
+    <t>0.9850,0.0125,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9824,0.0085,0.0012,0.0034</t>
+  </si>
+  <si>
+    <t>0.9662,0.0397,0.0035,0.0020</t>
+  </si>
+  <si>
+    <t>0.9835,0.0046,0.0015,0.0041</t>
+  </si>
+  <si>
+    <t>0.9818,0.0109,0.0024,0.0028</t>
+  </si>
+  <si>
+    <t>0.1638,0.1074,0.8090,0.0024</t>
+  </si>
+  <si>
+    <t>0.2608,0.4231,0.4114,0.0049</t>
+  </si>
+  <si>
+    <t>0.9197,0.0504,0.0074,0.0116</t>
+  </si>
+  <si>
+    <t>0.0356,0.0256,0.9606,0.0012</t>
+  </si>
+  <si>
+    <t>0.0022,0.0083,0.9904,0.0047</t>
+  </si>
+  <si>
+    <t>0.0493,0.0867,0.9134,0.0010</t>
+  </si>
+  <si>
+    <t>0.0022,0.0104,0.9957,0.0004</t>
+  </si>
+  <si>
+    <t>0.0875,0.1556,0.7936,0.0049</t>
+  </si>
+  <si>
+    <t>0.0048,0.0066,0.9887,0.0042</t>
+  </si>
+  <si>
+    <t>0.0158,0.0197,0.9646,0.0016</t>
+  </si>
+  <si>
+    <t>0.5198,0.0494,0.5212,0.0324</t>
+  </si>
+  <si>
+    <t>0.8792,0.0085,0.1219,0.0091</t>
+  </si>
+  <si>
+    <t>0.7783,0.0057,0.2995,0.0128</t>
+  </si>
+  <si>
+    <t>0.7830,0.0208,0.2263,0.0178</t>
+  </si>
+  <si>
+    <t>0.9798,0.0200,0.0011,0.0014</t>
+  </si>
+  <si>
+    <t>0.9839,0.0228,0.0015,0.0006</t>
+  </si>
+  <si>
+    <t>0.9893,0.0092,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.9425,0.0822,0.0038,0.0015</t>
+  </si>
+  <si>
+    <t>0.9865,0.0076,0.0008,0.0017</t>
+  </si>
+  <si>
+    <t>0.9837,0.0091,0.0022,0.0013</t>
+  </si>
+  <si>
+    <t>0.9538,0.0463,0.0090,0.0041</t>
+  </si>
+  <si>
+    <t>0.9811,0.0089,0.0013,0.0036</t>
+  </si>
+  <si>
+    <t>0.0140,0.2086,0.9367,0.0020</t>
+  </si>
+  <si>
+    <t>0.0338,0.0468,0.9412,0.0036</t>
+  </si>
+  <si>
+    <t>0.0232,0.4361,0.7933,0.0036</t>
+  </si>
+  <si>
+    <t>0.0665,0.7042,0.3546,0.0107</t>
+  </si>
+  <si>
+    <t>0.0144,0.0042,0.9756,0.0163</t>
+  </si>
+  <si>
+    <t>0.2400,0.0454,0.7679,0.0326</t>
+  </si>
+  <si>
+    <t>0.4913,0.0674,0.5429,0.0301</t>
+  </si>
+  <si>
+    <t>0.3255,0.0180,0.7054,0.0210</t>
+  </si>
+  <si>
+    <t>0.8143,0.0037,0.0102,0.1843</t>
+  </si>
+  <si>
+    <t>0.0223,0.0309,0.0021,0.9849</t>
+  </si>
+  <si>
+    <t>0.3513,0.0153,0.0325,0.6478</t>
+  </si>
+  <si>
+    <t>0.0084,0.0008,0.0013,0.9941</t>
+  </si>
+  <si>
+    <t>0.0049,0.0009,0.0004,0.9969</t>
+  </si>
+  <si>
+    <t>0.4694,0.0360,0.0507,0.4853</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1993,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2290,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2374,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2388,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2441,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2455,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2486,7 @@
         <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2575,7 +2584,7 @@
         <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,10 +2637,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,10 +2651,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2931,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,10 +2945,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,10 +2959,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2990,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3004,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3130,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3144,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,10 +3155,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3169,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,10 +3421,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,10 +3505,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3550,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3592,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3617,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3676,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3718,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3858,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,10 +4009,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4037,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4065,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4096,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4163,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,10 +4191,10 @@
         <v>259</v>
       </c>
       <c r="C161" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4359,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4390,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4628,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4656,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4684,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4698,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,10 +4709,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4726,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,10 +4737,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,10 +4905,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,10 +5101,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,10 +5171,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,10 +5367,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,10 +5381,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5412,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,10 +5423,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5521,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
